--- a/artfynd/A 49844-2025 artfynd.xlsx
+++ b/artfynd/A 49844-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136782845</v>
       </c>
       <c r="B2" t="n">
-        <v>96259</v>
+        <v>96261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136782844</v>
       </c>
       <c r="B3" t="n">
-        <v>96576</v>
+        <v>96578</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49844-2025 artfynd.xlsx
+++ b/artfynd/A 49844-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136782845</v>
       </c>
       <c r="B2" t="n">
-        <v>96261</v>
+        <v>96267</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136782844</v>
       </c>
       <c r="B3" t="n">
-        <v>96578</v>
+        <v>96584</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49844-2025 artfynd.xlsx
+++ b/artfynd/A 49844-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136782845</v>
       </c>
       <c r="B2" t="n">
-        <v>96267</v>
+        <v>96269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136782844</v>
       </c>
       <c r="B3" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49844-2025 artfynd.xlsx
+++ b/artfynd/A 49844-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136782845</v>
       </c>
       <c r="B2" t="n">
-        <v>96269</v>
+        <v>96270</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136782844</v>
       </c>
       <c r="B3" t="n">
-        <v>96586</v>
+        <v>96587</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49844-2025 artfynd.xlsx
+++ b/artfynd/A 49844-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136782845</v>
       </c>
       <c r="B2" t="n">
-        <v>96270</v>
+        <v>96276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136782844</v>
       </c>
       <c r="B3" t="n">
-        <v>96587</v>
+        <v>96593</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49844-2025 artfynd.xlsx
+++ b/artfynd/A 49844-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136782845</v>
       </c>
       <c r="B2" t="n">
-        <v>96276</v>
+        <v>96280</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136782844</v>
       </c>
       <c r="B3" t="n">
-        <v>96593</v>
+        <v>96597</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49844-2025 artfynd.xlsx
+++ b/artfynd/A 49844-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136782845</v>
       </c>
       <c r="B2" t="n">
-        <v>96280</v>
+        <v>96282</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136782844</v>
       </c>
       <c r="B3" t="n">
-        <v>96597</v>
+        <v>96599</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49844-2025 artfynd.xlsx
+++ b/artfynd/A 49844-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136782845</v>
       </c>
       <c r="B2" t="n">
-        <v>96282</v>
+        <v>96284</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136782844</v>
       </c>
       <c r="B3" t="n">
-        <v>96599</v>
+        <v>96601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49844-2025 artfynd.xlsx
+++ b/artfynd/A 49844-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136782845</v>
       </c>
       <c r="B2" t="n">
-        <v>96284</v>
+        <v>96297</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136782844</v>
       </c>
       <c r="B3" t="n">
-        <v>96601</v>
+        <v>96614</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49844-2025 artfynd.xlsx
+++ b/artfynd/A 49844-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136782845</v>
       </c>
       <c r="B2" t="n">
-        <v>96297</v>
+        <v>96299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136782844</v>
       </c>
       <c r="B3" t="n">
-        <v>96614</v>
+        <v>96616</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49844-2025 artfynd.xlsx
+++ b/artfynd/A 49844-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136782845</v>
       </c>
       <c r="B2" t="n">
-        <v>96299</v>
+        <v>96302</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136782844</v>
       </c>
       <c r="B3" t="n">
-        <v>96616</v>
+        <v>96619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49844-2025 artfynd.xlsx
+++ b/artfynd/A 49844-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136782845</v>
       </c>
       <c r="B2" t="n">
-        <v>96302</v>
+        <v>96312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136782844</v>
       </c>
       <c r="B3" t="n">
-        <v>96619</v>
+        <v>96629</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49844-2025 artfynd.xlsx
+++ b/artfynd/A 49844-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136782845</v>
       </c>
       <c r="B2" t="n">
-        <v>96312</v>
+        <v>96313</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136782844</v>
       </c>
       <c r="B3" t="n">
-        <v>96629</v>
+        <v>96630</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49844-2025 artfynd.xlsx
+++ b/artfynd/A 49844-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136782845</v>
       </c>
       <c r="B2" t="n">
-        <v>96313</v>
+        <v>96318</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136782844</v>
       </c>
       <c r="B3" t="n">
-        <v>96630</v>
+        <v>96635</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49844-2025 artfynd.xlsx
+++ b/artfynd/A 49844-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136782845</v>
       </c>
       <c r="B2" t="n">
-        <v>96318</v>
+        <v>96320</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136782844</v>
       </c>
       <c r="B3" t="n">
-        <v>96635</v>
+        <v>96637</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49844-2025 artfynd.xlsx
+++ b/artfynd/A 49844-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136782845</v>
       </c>
       <c r="B2" t="n">
-        <v>96320</v>
+        <v>96326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136782844</v>
       </c>
       <c r="B3" t="n">
-        <v>96637</v>
+        <v>96643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
